--- a/results/Int All Data 0.7/Linea_fi_all.xlsx
+++ b/results/Int All Data 0.7/Linea_fi_all.xlsx
@@ -1566,7 +1566,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.0004420432220039627 +/- 0.0028338647812871536</t>
+          <t>0.00039292730844796563 +/- 0.002776678590393417</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0012770137524557468 +/- 0.0013397035065801461</t>
+          <t>-0.0012278978388997608 +/- 0.0013761223699530333</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>0.0026790314270994653 +/- 0.000504789230867235</t>
+          <t>0.0025244719216898637 +/- 0.0004860371526047</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>0.0021454735740450647 +/- 0.0005463268712145751</t>
+          <t>0.002093144950287873 +/- 0.0006191606261747352</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.00633245382585752 +/- 0.0011318000311096254</t>
+          <t>-0.006385224274406331 +/- 0.001213720316622698</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>0.0011363636363636686 +/- 0.0009123609344179574</t>
+          <t>0.0010869565217391576 +/- 0.0009580394975131168</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="DX9" t="inlineStr">
         <is>
-          <t>0.02524096385542174 +/- 0.0029933152406758532</t>
+          <t>0.025301204819277168 +/- 0.003071698502164325</t>
         </is>
       </c>
       <c r="DY9" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>0.12795296632816683 +/- 0.006071393616745232</t>
+          <t>0.12800641368252277 +/- 0.006048058787774573</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="DP10" t="inlineStr">
         <is>
-          <t>0.09000534473543562 +/- 0.0022320270462662848</t>
+          <t>0.08995189738107966 +/- 0.0022172601296303073</t>
         </is>
       </c>
       <c r="DQ10" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>0.052699091394975986 +/- 0.003072176988391213</t>
+          <t>0.05285943345804386 +/- 0.0030182379269899366</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>0.004810261892036339 +/- 0.002725291028109454</t>
+          <t>0.004863709246392301 +/- 0.002832709780865854</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
